--- a/MVP-1/SRS/FlatWire_DevelopmentPlan.xlsx
+++ b/MVP-1/SRS/FlatWire_DevelopmentPlan.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read Me" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Delivery Options" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Delivery Summary" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plan by Stage" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprint Schedule" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Work Items" sheetId="5" state="visible" r:id="rId5"/>
@@ -16,8 +16,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions and Risks" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Plan by Stage'!$A$4:$J$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Work Items'!$A$4:$J$111</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Plan by Stage'!$A$4:$H$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Work Items'!$A$4:$H$107</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Assumptions and Risks'!$A$4:$C$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -156,11 +156,11 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -540,7 +540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -557,7 +557,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Issued August 13, 2026 · 15 stages · 107 work items · 186 days of development effort</t>
+          <t>Issued August 13, 2026 · 14 stages · 103 work items · 174 days of development effort</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
               <b val="1"/>
               <sz val="11"/>
             </rPr>
-            <t>186 days of development effort</t>
+            <t>174 days of development effort</t>
           </r>
           <r>
             <t xml:space="preserve"> across </t>
@@ -591,7 +591,7 @@
               <b val="1"/>
               <sz val="11"/>
             </rPr>
-            <t>107 work items</t>
+            <t>103 work items</t>
           </r>
           <r>
             <t xml:space="preserve">, grouped into </t>
@@ -602,7 +602,7 @@
               <b val="1"/>
               <sz val="11"/>
             </rPr>
-            <t>15 stages</t>
+            <t>14 stages</t>
           </r>
           <r>
             <t>.</t>
@@ -622,10 +622,10 @@
               <b val="1"/>
               <sz val="11"/>
             </rPr>
-            <t>Delivery Options</t>
+            <t>Delivery Summary</t>
           </r>
           <r>
-            <t xml:space="preserve"> — it is the decision that everything else follows from.</t>
+            <t xml:space="preserve"> — the date, and what would move it.</t>
           </r>
         </is>
       </c>
@@ -646,10 +646,10 @@
               <b val="1"/>
               <sz val="11"/>
             </rPr>
-            <t>Delivery Options</t>
+            <t>Delivery Summary</t>
           </r>
           <r>
-            <t xml:space="preserve"> — what each team size delivers, and what would change the date. Start here.</t>
+            <t xml:space="preserve"> — when development completes, and what would change that date. Start here.</t>
           </r>
         </is>
       </c>
@@ -666,7 +666,7 @@
             <t>Plan by Stage</t>
           </r>
           <r>
-            <t xml:space="preserve"> — the fifteen stages of the build, what each one gives you, and when each lands under each option.</t>
+            <t xml:space="preserve"> — the 14 stages of the build, what each one gives you, and the sprint each lands in.</t>
           </r>
         </is>
       </c>
@@ -683,7 +683,7 @@
             <t>Sprint Schedule</t>
           </r>
           <r>
-            <t xml:space="preserve"> — every two-week sprint under each option, with its dates, capacity and workload.</t>
+            <t xml:space="preserve"> — every two-week sprint, with its dates, capacity and workload.</t>
           </r>
         </is>
       </c>
@@ -758,7 +758,7 @@
             <t>Effort is in days, and a day is one person working for one day.</t>
           </r>
           <r>
-            <t xml:space="preserve"> Twenty days of effort is one person for four weeks, or four people for one week — it is a measure of size, not of elapsed time. The elapsed time is on the Delivery Options and Sprint Schedule sheets, and it depends entirely on how many people are working.</t>
+            <t xml:space="preserve"> Twenty days of effort is one person for four weeks, or four people for one week — it is a measure of size, not of elapsed time. The elapsed time is on the Delivery Summary and Sprint Schedule sheets, and it depends entirely on how many people are working.</t>
           </r>
         </is>
       </c>
@@ -810,6 +810,23 @@
               <b val="1"/>
               <sz val="11"/>
             </rPr>
+            <t>Coil yield, costing and scrap.</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> This work is out of the plan by agreement and no part of it is in any figure on these sheets. Yield would continue to be reported the way it is today, and flat wire scrap routed by hand, until it is picked up.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
             <t>Testing and business analysis.</t>
           </r>
           <r>
@@ -818,8 +835,8 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" s="4" t="inlineStr">
+    <row r="23">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -835,8 +852,8 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="B23" s="4" t="inlineStr">
+    <row r="24">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -852,29 +869,29 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>What we need back</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>A decision on team size — the Delivery Options sheet sets out the three we have costed and what each one delivers.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>The four items on the Milestones and Needs sheet marked as needed from you. Two of them gate work that starts early.</t>
+          <t>Confirmation of the team size the plan is built on, and of the completion date it produces. The Delivery Summary sheet sets out what would move that date.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>The four items on the Milestones and Needs sheet marked as needed from you. Two of them gate work that starts early.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>Confirmation that the stage order matches your operational priorities. If something matters more than its position suggests, it can be moved.</t>
         </is>
@@ -892,7 +909,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -905,14 +922,14 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Delivery Options</t>
+          <t>Delivery Summary</t>
         </is>
       </c>
     </row>
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>186 days of development effort. What that means depends on how many people are on it — the three options below are the ones we have costed.</t>
+          <t>174 days of development effort across 103 work items — the plan below is what that delivers, and when.</t>
         </is>
       </c>
     </row>
@@ -946,187 +963,164 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>2 developers</t>
+          <t>3 developers</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>Fri 8 Jan 2027</t>
+          <t>Wed 25 Nov 2026</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>+100 days</t>
+          <t>+56 days</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>misses the fourth quarter entirely</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>3 developers</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>Wed 25 Nov 2026</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="inlineStr">
-        <is>
-          <t>+56 days</t>
-        </is>
-      </c>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
           <t>inside the fourth quarter, no trial margin</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>4 developers</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>Fri 30 Oct 2026</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>+30 days</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>inside the fourth quarter, about 8 weeks of margin</t>
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>What changes the date</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Lever</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Effect on the date</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>What it means</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>What changes the date</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>Lever</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>Effect on the date</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>What it means</t>
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Complete the platform foundation before the sprints start</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Removes about two sprints.</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>The foundation is the largest single block of work and every later stage depends on it. Delivering it in the run-up rather than inside the sprints is the largest lever available by some distance — but it needs about five people during that period, which is more than the team this plan is built on.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>Let the final testing and commissioning stage start early</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>Removes one sprint — completion moves forward about two weeks.</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">The last sprint exists because end-to-end testing and machine commissioning are held to a window of their own, after everything they verify is finished. Overlapping that window with the preceding stage would recover two weeks, but it means testing against a system that is still changing. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>This is a decision to take deliberately, not a scheduling convenience.</t>
+          </r>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Defer the yield, cost and scrap work</t>
+          <t>Add a fourth developer</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Removes about half a sprint at three or four developers.</t>
+          <t>Removes one sprint — completion moves forward about two weeks.</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>This is the one phase that is wholly optional for go-live. Yield would be reported the existing way and flat wire scrap routed manually until it lands. It is the first thing we would cut and the last thing that affects an operator.</t>
+          <r>
+            <t xml:space="preserve">Only a fortnight, and that is the important part: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>the tail of the plan is waiting on dependencies, not on people.</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> A fourth developer leaves the last two sprints barely a third occupied, and a fifth brings completion only to the end of October. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>No team size reaches the end of September on this start date.</t>
+          </r>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>Complete the platform foundation before the sprints start</t>
+          <t>Accept the date the plan gives</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>Removes two to three sprints from every plan.</t>
+          <t>No change to scope or team.</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>The foundation is the largest single block of work and every later stage depends on it. Delivering it in the run-up rather than inside the sprints is the single biggest lever available — but it needs about five developers during that period, which is more than any option on this sheet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>Add a fifth developer</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>Brings development completion into early October.</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>Below about four people sustained, no team size reaches the end of September. Each person added shortens the plan roughly proportionally until the sequential dependencies between stages become the limit.</t>
+          <t>The plan lands inside the planned production window, though without margin for a trial. Moving the development completion date does not by itself move production, provided acceptance testing and stakeholder sign-off are scheduled after it rather than alongside it.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>Accept the date the plan gives</t>
-        </is>
-      </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>No change to scope or team.</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>All three options land inside or close to the planned production window. Moving the development completion date does not by itself move production, provided acceptance testing and commissioning are scheduled after it rather than alongside it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="11" t="inlineStr">
-        <is>
-          <t>Every option above uses the same scope and the same effort. The only variable is how many people are working on it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>These are development completion dates. Acceptance testing and machine commissioning follow them and are not included.</t>
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>This is a development completion date. Acceptance testing and machine commissioning follow it and are not included in it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>Coil yield, costing and scrap are out of the plan by agreement and are in none of these figures.</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1152,9 +1146,7 @@
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="44" customWidth="1" min="10" max="10"/>
+    <col width="44" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -1167,7 +1159,7 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>The 15 stages of the build, in delivery order. Each row is a block of capability that lands together.</t>
+          <t>The 14 stages of the build, in delivery order. Each row is a block of capability that lands together.</t>
         </is>
       </c>
     </row>
@@ -1204,20 +1196,10 @@
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>Sprint — 2 devs</t>
+          <t>Sprint</t>
         </is>
       </c>
       <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>Sprint — 3 devs</t>
-        </is>
-      </c>
-      <c r="I4" s="5" t="inlineStr">
-        <is>
-          <t>Sprint — 4 devs</t>
-        </is>
-      </c>
-      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>Can it be deferred?</t>
         </is>
@@ -1256,72 +1238,52 @@
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>No — every screen depends on it</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>Application services platform</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>The service that holds the business logic, the live-data feed to the screens, and the machine-write layer — including the simulation mode that lets every screen be built and demonstrated before the machines are wired.</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>Platform / foundation</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="F6" s="11" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G6" s="11" t="inlineStr">
+        <is>
           <t>S1–S2</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
-      <c r="I5" s="7" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
-      <c r="J5" s="6" t="inlineStr">
-        <is>
-          <t>No — every screen depends on it</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>Application services platform</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>The service that holds the business logic, the live-data feed to the screens, and the machine-write layer — including the simulation mode that lets every screen be built and demonstrated before the machines are wired.</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="inlineStr">
-        <is>
-          <t>Platform / foundation</t>
-        </is>
-      </c>
-      <c r="E6" s="10" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="F6" s="10" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="G6" s="10" t="inlineStr">
-        <is>
-          <t>S2–S3</t>
-        </is>
-      </c>
-      <c r="H6" s="10" t="inlineStr">
-        <is>
-          <t>S1–S2</t>
-        </is>
-      </c>
-      <c r="I6" s="10" t="inlineStr">
-        <is>
-          <t>S1–S2</t>
-        </is>
-      </c>
-      <c r="J6" s="9" t="inlineStr">
+      <c r="H6" s="11" t="inlineStr">
         <is>
           <t>No — every operation depends on it</t>
         </is>
@@ -1360,27 +1322,17 @@
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>S3–S4</t>
+          <t>S2–S3</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>S2–S3</t>
-        </is>
-      </c>
-      <c r="I7" s="7" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="J7" s="6" t="inlineStr">
-        <is>
           <t>No — nothing can be recorded without it</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -1400,32 +1352,22 @@
           <t>Supervisor</t>
         </is>
       </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="E8" s="11" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="F8" s="10" t="inlineStr">
+      <c r="F8" s="11" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G8" s="10" t="inlineStr">
-        <is>
-          <t>S4</t>
-        </is>
-      </c>
-      <c r="H8" s="10" t="inlineStr">
+      <c r="G8" s="11" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="I8" s="10" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="J8" s="9" t="inlineStr">
+      <c r="H8" s="11" t="inlineStr">
         <is>
           <t>No — every later stage consumes this live feed</t>
         </is>
@@ -1464,27 +1406,17 @@
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>S4–S5</t>
+          <t>S3</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>S3</t>
-        </is>
-      </c>
-      <c r="I9" s="7" t="inlineStr">
-        <is>
-          <t>S2–S3</t>
-        </is>
-      </c>
-      <c r="J9" s="6" t="inlineStr">
-        <is>
           <t>No — the entry point to every run</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -1504,32 +1436,22 @@
           <t>Line operator (FL1 and FL3)</t>
         </is>
       </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F10" s="10" t="inlineStr">
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G10" s="10" t="inlineStr">
-        <is>
-          <t>S5</t>
-        </is>
-      </c>
-      <c r="H10" s="10" t="inlineStr">
+      <c r="G10" s="11" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
       </c>
-      <c r="I10" s="10" t="inlineStr">
-        <is>
-          <t>S3</t>
-        </is>
-      </c>
-      <c r="J10" s="9" t="inlineStr">
+      <c r="H10" s="11" t="inlineStr">
         <is>
           <t>No — the operator has no view of the run without it</t>
         </is>
@@ -1568,27 +1490,17 @@
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>S5–S6</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>S4</t>
-        </is>
-      </c>
-      <c r="I11" s="7" t="inlineStr">
-        <is>
-          <t>S3</t>
-        </is>
-      </c>
-      <c r="J11" s="6" t="inlineStr">
-        <is>
           <t>Partly — individual events could follow go-live, at the cost of paper records</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -1608,32 +1520,22 @@
           <t>Line operator and supervisor</t>
         </is>
       </c>
-      <c r="E12" s="10" t="inlineStr">
+      <c r="E12" s="11" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="F12" s="10" t="inlineStr">
+      <c r="F12" s="11" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="G12" s="10" t="inlineStr">
-        <is>
-          <t>S6–S7</t>
-        </is>
-      </c>
-      <c r="H12" s="10" t="inlineStr">
+      <c r="G12" s="11" t="inlineStr">
         <is>
           <t>S4–S5</t>
         </is>
       </c>
-      <c r="I12" s="10" t="inlineStr">
-        <is>
-          <t>S4</t>
-        </is>
-      </c>
-      <c r="J12" s="9" t="inlineStr">
+      <c r="H12" s="11" t="inlineStr">
         <is>
           <t>Partly — the material hold could follow go-live; checkout could not</t>
         </is>
@@ -1672,72 +1574,52 @@
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>S7</t>
+          <t>S5</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
+          <t>No — the finishing line cannot be run without it</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>Coil completion, labelling and packing</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>The finish line — confirm the coil, record which rods produced which footage, calculate the weight, print the label and manage the two-coils-per-skid packing rule.</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>Line operator and packing operator</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F14" s="11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G14" s="11" t="inlineStr">
+        <is>
           <t>S5</t>
         </is>
       </c>
-      <c r="I13" s="7" t="inlineStr">
-        <is>
-          <t>S4</t>
-        </is>
-      </c>
-      <c r="J13" s="6" t="inlineStr">
-        <is>
-          <t>No — the finishing line cannot be run without it</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>Coil completion, labelling and packing</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>The finish line — confirm the coil, record which rods produced which footage, calculate the weight, print the label and manage the two-coils-per-skid packing rule.</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="inlineStr">
-        <is>
-          <t>Line operator and packing operator</t>
-        </is>
-      </c>
-      <c r="E14" s="10" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="F14" s="10" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="G14" s="10" t="inlineStr">
-        <is>
-          <t>S8</t>
-        </is>
-      </c>
-      <c r="H14" s="10" t="inlineStr">
-        <is>
-          <t>S5</t>
-        </is>
-      </c>
-      <c r="I14" s="10" t="inlineStr">
-        <is>
-          <t>S4</t>
-        </is>
-      </c>
-      <c r="J14" s="9" t="inlineStr">
+      <c r="H14" s="11" t="inlineStr">
         <is>
           <t>No — there is no finished coil without it</t>
         </is>
@@ -1776,27 +1658,17 @@
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>S8</t>
+          <t>S5–S6</t>
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>S5–S6</t>
-        </is>
-      </c>
-      <c r="I15" s="7" t="inlineStr">
-        <is>
-          <t>S4</t>
-        </is>
-      </c>
-      <c r="J15" s="6" t="inlineStr">
-        <is>
           <t>No — the hybrid route would not exist</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -1816,32 +1688,22 @@
           <t>Quality and process engineering</t>
         </is>
       </c>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="E16" s="11" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F16" s="10" t="inlineStr">
+      <c r="F16" s="11" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G16" s="10" t="inlineStr">
-        <is>
-          <t>S8–S9</t>
-        </is>
-      </c>
-      <c r="H16" s="10" t="inlineStr">
+      <c r="G16" s="11" t="inlineStr">
         <is>
           <t>S6</t>
         </is>
       </c>
-      <c r="I16" s="10" t="inlineStr">
-        <is>
-          <t>S4–S5</t>
-        </is>
-      </c>
-      <c r="J16" s="9" t="inlineStr">
+      <c r="H16" s="11" t="inlineStr">
         <is>
           <t>Partly — reporting could follow go-live; the certificate could not</t>
         </is>
@@ -1880,145 +1742,73 @@
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>S9</t>
+          <t>S6</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>S6</t>
-        </is>
-      </c>
-      <c r="I17" s="7" t="inlineStr">
-        <is>
-          <t>S5</t>
-        </is>
-      </c>
-      <c r="J17" s="6" t="inlineStr">
-        <is>
           <t>Partly — reference data could be loaded by hand at first</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Yield, cost and scrap</t>
+          <t>Integration testing, commissioning and go-live</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>Yield measured the way flat wire is actually produced, cost standards for the new lines, and scrap routed like every other material.</t>
+          <t>The convergence — full end-to-end runs of all three routes, machine commissioning support, acceptance testing and the move to production.</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>Production control and cost accounting</t>
-        </is>
-      </c>
-      <c r="E18" s="10" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="F18" s="10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G18" s="10" t="inlineStr">
-        <is>
-          <t>S9–S10</t>
-        </is>
-      </c>
-      <c r="H18" s="10" t="inlineStr">
-        <is>
-          <t>S6</t>
-        </is>
-      </c>
-      <c r="I18" s="10" t="inlineStr">
-        <is>
-          <t>S5</t>
-        </is>
-      </c>
-      <c r="J18" s="9" t="inlineStr">
-        <is>
-          <t>Yes — wholly optional for go-live, and the first thing we would cut</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>Integration testing, commissioning and go-live</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>The convergence — full end-to-end runs of all three routes, machine commissioning support, acceptance testing and the move to production.</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
           <t>Quality assurance and commissioning</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="E18" s="11" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="F19" s="7" t="inlineStr">
+      <c r="F18" s="11" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G19" s="7" t="inlineStr">
-        <is>
-          <t>S10</t>
-        </is>
-      </c>
-      <c r="H19" s="7" t="inlineStr">
+      <c r="G18" s="11" t="inlineStr">
         <is>
           <t>S7</t>
         </is>
       </c>
-      <c r="I19" s="7" t="inlineStr">
-        <is>
-          <t>S5</t>
-        </is>
-      </c>
-      <c r="J19" s="6" t="inlineStr">
+      <c r="H18" s="11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>Stage effort is rounded to whole days, so the column sums to within a day of the 174-day total rather than exactly to it.</t>
+        </is>
+      </c>
+    </row>
     <row r="21">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t>Stage effort is rounded to whole days, so the column sums to within a day of the 186-day total rather than exactly to it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="11" t="inlineStr">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>A sprint range means the stage spans those sprints; it does not occupy them exclusively — several stages run alongside each other.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J19"/>
+  <autoFilter ref="A4:H18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2030,7 +1820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2060,7 +1850,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2 developers — 10 sprints, development complete Fri 8 Jan 2027</t>
+          <t>3 developers — 7 sprints, development complete Wed 25 Nov 2026</t>
         </is>
       </c>
     </row>
@@ -2124,32 +1914,32 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>31</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>101 %</t>
+          <t>102 %</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>Operator screen platform</t>
+          <t>Operator screen platform · Application services platform</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -2159,34 +1949,34 @@
           <t>07 Sep – 18 Sep</t>
         </is>
       </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="C7" s="11" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D7" s="10" t="inlineStr">
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="inlineStr">
+        <is>
+          <t>96 %</t>
+        </is>
+      </c>
+      <c r="G7" s="11" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E7" s="10" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="F7" s="10" t="inlineStr">
-        <is>
-          <t>92 %</t>
-        </is>
-      </c>
-      <c r="G7" s="10" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="H7" s="9" t="inlineStr">
         <is>
-          <t>Operator screen platform · Application services platform</t>
+          <t>Application services platform · Data foundation</t>
         </is>
       </c>
     </row>
@@ -2208,69 +1998,69 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>99 %</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>Data foundation · Line status board and live data · Rod check-in and machine configuration</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>S4</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>05 Oct – 16 Oct</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="inlineStr">
+        <is>
+          <t>102 %</t>
+        </is>
+      </c>
+      <c r="G9" s="11" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>100 %</t>
-        </is>
-      </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>Application services platform · Data foundation</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>S4</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t>05 Oct – 16 Oct</t>
-        </is>
-      </c>
-      <c r="C9" s="10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D9" s="10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E9" s="10" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="F9" s="10" t="inlineStr">
-        <is>
-          <t>104 %</t>
-        </is>
-      </c>
-      <c r="G9" s="10" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="H9" s="9" t="inlineStr">
         <is>
-          <t>Data foundation · Line status board and live data · Rod check-in and machine configuration</t>
+          <t>Active run monitoring · In-run production events · Exception handling</t>
         </is>
       </c>
     </row>
@@ -2292,12 +2082,12 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -2307,17 +2097,17 @@
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>21</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>Rod check-in and machine configuration · Active run monitoring · In-run production events</t>
+          <t>Exception handling · Spool check-in and finishing run · Coil completion, labelling and packing · Hybrid continuous operation</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>S6</t>
         </is>
@@ -2327,34 +2117,34 @@
           <t>02 Nov – 13 Nov</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C11" s="11" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E11" s="10" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="F11" s="10" t="inlineStr">
-        <is>
-          <t>97 %</t>
-        </is>
-      </c>
-      <c r="G11" s="10" t="inlineStr">
-        <is>
-          <t>13</t>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F11" s="11" t="inlineStr">
+        <is>
+          <t>60 %</t>
+        </is>
+      </c>
+      <c r="G11" s="11" t="inlineStr">
+        <is>
+          <t>15</t>
         </is>
       </c>
       <c r="H11" s="9" t="inlineStr">
         <is>
-          <t>In-run production events · Exception handling</t>
+          <t>Hybrid continuous operation · Reporting and certification · Administration and reference data</t>
         </is>
       </c>
     </row>
@@ -2376,900 +2166,88 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>24</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>97 %</t>
+          <t>36 %</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>Exception handling · Spool check-in and finishing run</t>
+          <t>Integration testing, commissioning and go-live</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>S8</t>
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>Total</t>
         </is>
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>30 Nov – 11 Dec</t>
-        </is>
-      </c>
-      <c r="C13" s="10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E13" s="10" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="F13" s="10" t="inlineStr">
-        <is>
-          <t>103 %</t>
-        </is>
-      </c>
-      <c r="G13" s="10" t="inlineStr">
-        <is>
-          <t>13</t>
+          <t>24 Aug – 25 Nov 2026</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="F13" s="11" t="inlineStr">
+        <is>
+          <t>87 %</t>
+        </is>
+      </c>
+      <c r="G13" s="11" t="inlineStr">
+        <is>
+          <t>103</t>
         </is>
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>Coil completion, labelling and packing · Hybrid continuous operation · Reporting and certification</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>S9</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>14 Dec – 23 Dec</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>104 %</t>
-        </is>
-      </c>
-      <c r="G14" s="7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>Reporting and certification · Administration and reference data · Yield, cost and scrap</t>
+          <t>the whole plan</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>S10</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>28 Dec – 08 Jan</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="D15" s="10" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="E15" s="10" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="F15" s="10" t="inlineStr">
-        <is>
-          <t>88 %</t>
-        </is>
-      </c>
-      <c r="G15" s="10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H15" s="9" t="inlineStr">
-        <is>
-          <t>Yield, cost and scrap · Integration testing, commissioning and go-live</t>
+          <t>Team capacity is the whole team for the whole sprint; planned work is the effort of the items placed in it. Utilisation is one against the other.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>24 Aug – 08 Jan 2027</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>99 %</t>
-        </is>
-      </c>
-      <c r="G16" s="7" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>the whole plan</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>3 developers — 7 sprints, development complete Wed 25 Nov 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>Sprint</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>Dates</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>Working days</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>Team capacity (days)</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>Planned work (days)</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>Utilisation</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>Work items</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>What is delivered</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>24 Aug – 04 Sep</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="F20" s="7" t="inlineStr">
-        <is>
-          <t>102 %</t>
-        </is>
-      </c>
-      <c r="G20" s="7" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="H20" s="6" t="inlineStr">
-        <is>
-          <t>Operator screen platform · Application services platform</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="10" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>07 Sep – 18 Sep</t>
-        </is>
-      </c>
-      <c r="C21" s="10" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E21" s="10" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="F21" s="10" t="inlineStr">
-        <is>
-          <t>96 %</t>
-        </is>
-      </c>
-      <c r="G21" s="10" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="H21" s="9" t="inlineStr">
-        <is>
-          <t>Application services platform · Data foundation</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>S3</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>21 Sep – 02 Oct</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="F22" s="7" t="inlineStr">
-        <is>
-          <t>99 %</t>
-        </is>
-      </c>
-      <c r="G22" s="7" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t>Data foundation · Line status board and live data · Rod check-in and machine configuration</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="10" t="inlineStr">
-        <is>
-          <t>S4</t>
-        </is>
-      </c>
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>05 Oct – 16 Oct</t>
-        </is>
-      </c>
-      <c r="C23" s="10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D23" s="10" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="E23" s="10" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="F23" s="10" t="inlineStr">
-        <is>
-          <t>102 %</t>
-        </is>
-      </c>
-      <c r="G23" s="10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="H23" s="9" t="inlineStr">
-        <is>
-          <t>Active run monitoring · In-run production events · Exception handling</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>S5</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>19 Oct – 30 Oct</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>102 %</t>
-        </is>
-      </c>
-      <c r="G24" s="7" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="H24" s="6" t="inlineStr">
-        <is>
-          <t>Exception handling · Spool check-in and finishing run · Coil completion, labelling and packing · Hybrid continuous operation</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="10" t="inlineStr">
-        <is>
-          <t>S6</t>
-        </is>
-      </c>
-      <c r="B25" s="9" t="inlineStr">
-        <is>
-          <t>02 Nov – 13 Nov</t>
-        </is>
-      </c>
-      <c r="C25" s="10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D25" s="10" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="E25" s="10" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="F25" s="10" t="inlineStr">
-        <is>
-          <t>98 %</t>
-        </is>
-      </c>
-      <c r="G25" s="10" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="H25" s="9" t="inlineStr">
-        <is>
-          <t>Hybrid continuous operation · Reporting and certification · Administration and reference data · Yield, cost and scrap</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>S7</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>16 Nov – 25 Nov</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="E26" s="7" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="F26" s="7" t="inlineStr">
-        <is>
-          <t>36 %</t>
-        </is>
-      </c>
-      <c r="G26" s="7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H26" s="6" t="inlineStr">
-        <is>
-          <t>Integration testing, commissioning and go-live</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="10" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B27" s="9" t="inlineStr">
-        <is>
-          <t>24 Aug – 25 Nov 2026</t>
-        </is>
-      </c>
-      <c r="C27" s="10" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="D27" s="10" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
-      <c r="E27" s="10" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="F27" s="10" t="inlineStr">
-        <is>
-          <t>92 %</t>
-        </is>
-      </c>
-      <c r="G27" s="10" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="H27" s="9" t="inlineStr">
-        <is>
-          <t>the whole plan</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>4 developers — 5 sprints, development complete Fri 30 Oct 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>Sprint</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>Dates</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>Working days</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>Team capacity (days)</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>Planned work (days)</t>
-        </is>
-      </c>
-      <c r="F30" s="5" t="inlineStr">
-        <is>
-          <t>Utilisation</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="inlineStr">
-        <is>
-          <t>Work items</t>
-        </is>
-      </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>What is delivered</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>24 Aug – 04 Sep</t>
-        </is>
-      </c>
-      <c r="C31" s="7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="F31" s="7" t="inlineStr">
-        <is>
-          <t>98 %</t>
-        </is>
-      </c>
-      <c r="G31" s="7" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="H31" s="6" t="inlineStr">
-        <is>
-          <t>Operator screen platform · Application services platform</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="10" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="B32" s="9" t="inlineStr">
-        <is>
-          <t>07 Sep – 18 Sep</t>
-        </is>
-      </c>
-      <c r="C32" s="10" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="D32" s="10" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="E32" s="10" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="F32" s="10" t="inlineStr">
-        <is>
-          <t>97 %</t>
-        </is>
-      </c>
-      <c r="G32" s="10" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="H32" s="9" t="inlineStr">
-        <is>
-          <t>Application services platform · Data foundation · Line status board and live data · Rod check-in and machine configuration</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>S3</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>21 Sep – 02 Oct</t>
-        </is>
-      </c>
-      <c r="C33" s="7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D33" s="7" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="E33" s="7" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="F33" s="7" t="inlineStr">
-        <is>
-          <t>98 %</t>
-        </is>
-      </c>
-      <c r="G33" s="7" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="H33" s="6" t="inlineStr">
-        <is>
-          <t>Rod check-in and machine configuration · Active run monitoring · In-run production events</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="10" t="inlineStr">
-        <is>
-          <t>S4</t>
-        </is>
-      </c>
-      <c r="B34" s="9" t="inlineStr">
-        <is>
-          <t>05 Oct – 16 Oct</t>
-        </is>
-      </c>
-      <c r="C34" s="10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D34" s="10" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="E34" s="10" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="F34" s="10" t="inlineStr">
-        <is>
-          <t>99 %</t>
-        </is>
-      </c>
-      <c r="G34" s="10" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="H34" s="9" t="inlineStr">
-        <is>
-          <t>Exception handling · Spool check-in and finishing run · Coil completion, labelling and packing · Hybrid continuous operation · Reporting and certification</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t>S5</t>
-        </is>
-      </c>
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>19 Oct – 30 Oct</t>
-        </is>
-      </c>
-      <c r="C35" s="7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="F35" s="7" t="inlineStr">
-        <is>
-          <t>81 %</t>
-        </is>
-      </c>
-      <c r="G35" s="7" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="H35" s="6" t="inlineStr">
-        <is>
-          <t>Reporting and certification · Administration and reference data · Yield, cost and scrap · Integration testing, commissioning and go-live</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="10" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B36" s="9" t="inlineStr">
-        <is>
-          <t>24 Aug – 30 Oct 2026</t>
-        </is>
-      </c>
-      <c r="C36" s="10" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="D36" s="10" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
-      <c r="E36" s="10" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="F36" s="10" t="inlineStr">
-        <is>
-          <t>95 %</t>
-        </is>
-      </c>
-      <c r="G36" s="10" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="H36" s="9" t="inlineStr">
-        <is>
-          <t>the whole plan</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="11" t="inlineStr">
-        <is>
-          <t>Team capacity is the whole team for the whole sprint; planned work is the effort of the items placed in it. Utilisation is one against the other.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="11" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>Above 100 % means the sprint is planned slightly over capacity and absorbs the difference from the sprint before or after it.</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="11" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>A short final sprint is the tail of the plan, not spare capacity — the work left in it cannot start any earlier.</t>
         </is>
@@ -3287,7 +2265,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J111"/>
+  <dimension ref="A1:H107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3298,8 +2276,6 @@
     <col width="30" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -3312,7 +2288,7 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>All 107 items of development work, in the order they are built. Use the filters on the header row to narrow to a stage or a sprint.</t>
+          <t>All 103 items of development work, in the order they are built. Use the filters on the header row to narrow to a stage or a sprint.</t>
         </is>
       </c>
     </row>
@@ -3354,17 +2330,7 @@
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>Sprint — 2 devs</t>
-        </is>
-      </c>
-      <c r="I4" s="5" t="inlineStr">
-        <is>
-          <t>Sprint — 3 devs</t>
-        </is>
-      </c>
-      <c r="J4" s="5" t="inlineStr">
-        <is>
-          <t>Sprint — 4 devs</t>
+          <t>Sprint</t>
         </is>
       </c>
     </row>
@@ -3409,19 +2375,9 @@
           <t>S1</t>
         </is>
       </c>
-      <c r="I5" s="7" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
-      <c r="J5" s="7" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -3451,22 +2407,12 @@
           <t>Operator screens</t>
         </is>
       </c>
-      <c r="G6" s="10" t="inlineStr">
+      <c r="G6" s="11" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="H6" s="10" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
-      <c r="I6" s="10" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
-      <c r="J6" s="10" t="inlineStr">
+      <c r="H6" s="11" t="inlineStr">
         <is>
           <t>S1</t>
         </is>
@@ -3513,19 +2459,9 @@
           <t>S1</t>
         </is>
       </c>
-      <c r="I7" s="7" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
-      <c r="J7" s="7" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -3555,22 +2491,12 @@
           <t>Operator screens</t>
         </is>
       </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="G8" s="11" t="inlineStr">
         <is>
           <t>9.4</t>
         </is>
       </c>
-      <c r="H8" s="10" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
-      <c r="I8" s="10" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
-      <c r="J8" s="10" t="inlineStr">
+      <c r="H8" s="11" t="inlineStr">
         <is>
           <t>S1</t>
         </is>
@@ -3617,19 +2543,9 @@
           <t>S1</t>
         </is>
       </c>
-      <c r="I9" s="7" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
-      <c r="J9" s="7" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -3659,22 +2575,12 @@
           <t>Live data and machine interface</t>
         </is>
       </c>
-      <c r="G10" s="10" t="inlineStr">
+      <c r="G10" s="11" t="inlineStr">
         <is>
           <t>1.9</t>
         </is>
       </c>
-      <c r="H10" s="10" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
-      <c r="I10" s="10" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
-      <c r="J10" s="10" t="inlineStr">
+      <c r="H10" s="11" t="inlineStr">
         <is>
           <t>S1</t>
         </is>
@@ -3721,19 +2627,9 @@
           <t>S1</t>
         </is>
       </c>
-      <c r="I11" s="7" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
-      <c r="J11" s="7" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -3763,22 +2659,12 @@
           <t>Live data and machine interface</t>
         </is>
       </c>
-      <c r="G12" s="10" t="inlineStr">
+      <c r="G12" s="11" t="inlineStr">
         <is>
           <t>0.6</t>
         </is>
       </c>
-      <c r="H12" s="10" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="I12" s="10" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
-      <c r="J12" s="10" t="inlineStr">
+      <c r="H12" s="11" t="inlineStr">
         <is>
           <t>S1</t>
         </is>
@@ -3825,19 +2711,9 @@
           <t>S1</t>
         </is>
       </c>
-      <c r="I13" s="7" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
-      <c r="J13" s="7" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -3867,24 +2743,14 @@
           <t>Live data and machine interface</t>
         </is>
       </c>
-      <c r="G14" s="10" t="inlineStr">
+      <c r="G14" s="11" t="inlineStr">
         <is>
           <t>2.8</t>
         </is>
       </c>
-      <c r="H14" s="10" t="inlineStr">
-        <is>
-          <t>S3</t>
-        </is>
-      </c>
-      <c r="I14" s="10" t="inlineStr">
+      <c r="H14" s="11" t="inlineStr">
         <is>
           <t>S2</t>
-        </is>
-      </c>
-      <c r="J14" s="10" t="inlineStr">
-        <is>
-          <t>S1</t>
         </is>
       </c>
     </row>
@@ -3926,22 +2792,12 @@
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="I15" s="7" t="inlineStr">
-        <is>
           <t>S1</t>
         </is>
       </c>
-      <c r="J15" s="7" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -3971,22 +2827,12 @@
           <t>Application services</t>
         </is>
       </c>
-      <c r="G16" s="10" t="inlineStr">
+      <c r="G16" s="11" t="inlineStr">
         <is>
           <t>1.4</t>
         </is>
       </c>
-      <c r="H16" s="10" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="I16" s="10" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
-      <c r="J16" s="10" t="inlineStr">
+      <c r="H16" s="11" t="inlineStr">
         <is>
           <t>S1</t>
         </is>
@@ -4030,22 +2876,12 @@
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="I17" s="7" t="inlineStr">
-        <is>
           <t>S1</t>
         </is>
       </c>
-      <c r="J17" s="7" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>14</t>
         </is>
@@ -4075,22 +2911,12 @@
           <t>Application services</t>
         </is>
       </c>
-      <c r="G18" s="10" t="inlineStr">
+      <c r="G18" s="11" t="inlineStr">
         <is>
           <t>1.8</t>
         </is>
       </c>
-      <c r="H18" s="10" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="I18" s="10" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
-      <c r="J18" s="10" t="inlineStr">
+      <c r="H18" s="11" t="inlineStr">
         <is>
           <t>S1</t>
         </is>
@@ -4137,19 +2963,9 @@
           <t>S2</t>
         </is>
       </c>
-      <c r="I19" s="7" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="J19" s="7" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>16</t>
         </is>
@@ -4179,22 +2995,12 @@
           <t>Application services</t>
         </is>
       </c>
-      <c r="G20" s="10" t="inlineStr">
+      <c r="G20" s="11" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="H20" s="10" t="inlineStr">
-        <is>
-          <t>S3</t>
-        </is>
-      </c>
-      <c r="I20" s="10" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="J20" s="10" t="inlineStr">
+      <c r="H20" s="11" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -4241,66 +3047,46 @@
           <t>S2</t>
         </is>
       </c>
-      <c r="I21" s="7" t="inlineStr">
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>Role-based access rules</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>Each action admits only the roles that should be able to perform it — operator, supervisor, operations manager, quality, engineering.</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>Application services platform</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>Platform / foundation</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>Application services</t>
+        </is>
+      </c>
+      <c r="G22" s="11" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="H22" s="11" t="inlineStr">
         <is>
           <t>S2</t>
-        </is>
-      </c>
-      <c r="J21" s="7" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>Role-based access rules</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>Each action admits only the roles that should be able to perform it — operator, supervisor, operations manager, quality, engineering.</t>
-        </is>
-      </c>
-      <c r="D22" s="9" t="inlineStr">
-        <is>
-          <t>Application services platform</t>
-        </is>
-      </c>
-      <c r="E22" s="9" t="inlineStr">
-        <is>
-          <t>Platform / foundation</t>
-        </is>
-      </c>
-      <c r="F22" s="9" t="inlineStr">
-        <is>
-          <t>Application services</t>
-        </is>
-      </c>
-      <c r="G22" s="10" t="inlineStr">
-        <is>
-          <t>1.4</t>
-        </is>
-      </c>
-      <c r="H22" s="10" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="I22" s="10" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="J22" s="10" t="inlineStr">
-        <is>
-          <t>S1</t>
         </is>
       </c>
     </row>
@@ -4345,66 +3131,46 @@
           <t>S2</t>
         </is>
       </c>
-      <c r="I23" s="7" t="inlineStr">
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>One definition per business value</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>A status or category means exactly the same thing on the screen, in the service and in the database — they cannot drift apart.</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>Application services platform</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>Platform / foundation</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>Application services</t>
+        </is>
+      </c>
+      <c r="G24" s="11" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="H24" s="11" t="inlineStr">
         <is>
           <t>S2</t>
-        </is>
-      </c>
-      <c r="J23" s="7" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t>One definition per business value</t>
-        </is>
-      </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>A status or category means exactly the same thing on the screen, in the service and in the database — they cannot drift apart.</t>
-        </is>
-      </c>
-      <c r="D24" s="9" t="inlineStr">
-        <is>
-          <t>Application services platform</t>
-        </is>
-      </c>
-      <c r="E24" s="9" t="inlineStr">
-        <is>
-          <t>Platform / foundation</t>
-        </is>
-      </c>
-      <c r="F24" s="9" t="inlineStr">
-        <is>
-          <t>Application services</t>
-        </is>
-      </c>
-      <c r="G24" s="10" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="H24" s="10" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="I24" s="10" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="J24" s="10" t="inlineStr">
-        <is>
-          <t>S1</t>
         </is>
       </c>
     </row>
@@ -4446,22 +3212,12 @@
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>S3</t>
-        </is>
-      </c>
-      <c r="I25" s="7" t="inlineStr">
-        <is>
           <t>S2</t>
         </is>
       </c>
-      <c r="J25" s="7" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="inlineStr">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t>22</t>
         </is>
@@ -4491,22 +3247,12 @@
           <t>Live data and machine interface</t>
         </is>
       </c>
-      <c r="G26" s="10" t="inlineStr">
+      <c r="G26" s="11" t="inlineStr">
         <is>
           <t>1.4</t>
         </is>
       </c>
-      <c r="H26" s="10" t="inlineStr">
-        <is>
-          <t>S3</t>
-        </is>
-      </c>
-      <c r="I26" s="10" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="J26" s="10" t="inlineStr">
+      <c r="H26" s="11" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -4550,22 +3296,12 @@
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>S3</t>
-        </is>
-      </c>
-      <c r="I27" s="7" t="inlineStr">
-        <is>
           <t>S2</t>
         </is>
       </c>
-      <c r="J27" s="7" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="A28" s="11" t="inlineStr">
         <is>
           <t>24</t>
         </is>
@@ -4595,22 +3331,12 @@
           <t>Live data and machine interface</t>
         </is>
       </c>
-      <c r="G28" s="10" t="inlineStr">
+      <c r="G28" s="11" t="inlineStr">
         <is>
           <t>1.4</t>
         </is>
       </c>
-      <c r="H28" s="10" t="inlineStr">
-        <is>
-          <t>S3</t>
-        </is>
-      </c>
-      <c r="I28" s="10" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="J28" s="10" t="inlineStr">
+      <c r="H28" s="11" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -4654,22 +3380,12 @@
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="I29" s="7" t="inlineStr">
-        <is>
           <t>S1</t>
         </is>
       </c>
-      <c r="J29" s="7" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="inlineStr">
+      <c r="A30" s="11" t="inlineStr">
         <is>
           <t>26</t>
         </is>
@@ -4699,22 +3415,12 @@
           <t>Live data and machine interface</t>
         </is>
       </c>
-      <c r="G30" s="10" t="inlineStr">
+      <c r="G30" s="11" t="inlineStr">
         <is>
           <t>2.8</t>
         </is>
       </c>
-      <c r="H30" s="10" t="inlineStr">
-        <is>
-          <t>S3</t>
-        </is>
-      </c>
-      <c r="I30" s="10" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="J30" s="10" t="inlineStr">
+      <c r="H30" s="11" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -4758,22 +3464,12 @@
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>S3</t>
-        </is>
-      </c>
-      <c r="I31" s="7" t="inlineStr">
-        <is>
           <t>S2</t>
         </is>
       </c>
-      <c r="J31" s="7" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="inlineStr">
+      <c r="A32" s="11" t="inlineStr">
         <is>
           <t>28</t>
         </is>
@@ -4803,22 +3499,12 @@
           <t>Data</t>
         </is>
       </c>
-      <c r="G32" s="10" t="inlineStr">
+      <c r="G32" s="11" t="inlineStr">
         <is>
           <t>0.4</t>
         </is>
       </c>
-      <c r="H32" s="10" t="inlineStr">
-        <is>
-          <t>S3</t>
-        </is>
-      </c>
-      <c r="I32" s="10" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="J32" s="10" t="inlineStr">
+      <c r="H32" s="11" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -4862,22 +3548,12 @@
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>S3</t>
-        </is>
-      </c>
-      <c r="I33" s="7" t="inlineStr">
-        <is>
           <t>S2</t>
         </is>
       </c>
-      <c r="J33" s="7" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="inlineStr">
+      <c r="A34" s="11" t="inlineStr">
         <is>
           <t>30</t>
         </is>
@@ -4907,22 +3583,12 @@
           <t>Data</t>
         </is>
       </c>
-      <c r="G34" s="10" t="inlineStr">
+      <c r="G34" s="11" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="H34" s="10" t="inlineStr">
-        <is>
-          <t>S3</t>
-        </is>
-      </c>
-      <c r="I34" s="10" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="J34" s="10" t="inlineStr">
+      <c r="H34" s="11" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -4966,69 +3632,49 @@
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
+          <t>S2</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>Production event and output records</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>Business rules stated in the specification are enforced by the database itself, so they cannot be bypassed.</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>Data foundation</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t>Platform / foundation</t>
+        </is>
+      </c>
+      <c r="F36" s="9" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="G36" s="11" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
+      </c>
+      <c r="H36" s="11" t="inlineStr">
+        <is>
           <t>S3</t>
-        </is>
-      </c>
-      <c r="I35" s="7" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="J35" s="7" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="10" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B36" s="9" t="inlineStr">
-        <is>
-          <t>Production event and output records</t>
-        </is>
-      </c>
-      <c r="C36" s="9" t="inlineStr">
-        <is>
-          <t>Business rules stated in the specification are enforced by the database itself, so they cannot be bypassed.</t>
-        </is>
-      </c>
-      <c r="D36" s="9" t="inlineStr">
-        <is>
-          <t>Data foundation</t>
-        </is>
-      </c>
-      <c r="E36" s="9" t="inlineStr">
-        <is>
-          <t>Platform / foundation</t>
-        </is>
-      </c>
-      <c r="F36" s="9" t="inlineStr">
-        <is>
-          <t>Data</t>
-        </is>
-      </c>
-      <c r="G36" s="10" t="inlineStr">
-        <is>
-          <t>3.9</t>
-        </is>
-      </c>
-      <c r="H36" s="10" t="inlineStr">
-        <is>
-          <t>S4</t>
-        </is>
-      </c>
-      <c r="I36" s="10" t="inlineStr">
-        <is>
-          <t>S3</t>
-        </is>
-      </c>
-      <c r="J36" s="10" t="inlineStr">
-        <is>
-          <t>S2</t>
         </is>
       </c>
     </row>
@@ -5070,69 +3716,49 @@
       </c>
       <c r="H37" s="7" t="inlineStr">
         <is>
+          <t>S2</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>Line status board</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>Floor-wide awareness of all three lines from one screen, without walking the floor.</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>Line status board and live data</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="inlineStr">
+        <is>
+          <t>Supervisor</t>
+        </is>
+      </c>
+      <c r="F38" s="9" t="inlineStr">
+        <is>
+          <t>Operator screens</t>
+        </is>
+      </c>
+      <c r="G38" s="11" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
+      </c>
+      <c r="H38" s="11" t="inlineStr">
+        <is>
           <t>S3</t>
-        </is>
-      </c>
-      <c r="I37" s="7" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="J37" s="7" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="10" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="B38" s="9" t="inlineStr">
-        <is>
-          <t>Line status board</t>
-        </is>
-      </c>
-      <c r="C38" s="9" t="inlineStr">
-        <is>
-          <t>Floor-wide awareness of all three lines from one screen, without walking the floor.</t>
-        </is>
-      </c>
-      <c r="D38" s="9" t="inlineStr">
-        <is>
-          <t>Line status board and live data</t>
-        </is>
-      </c>
-      <c r="E38" s="9" t="inlineStr">
-        <is>
-          <t>Supervisor</t>
-        </is>
-      </c>
-      <c r="F38" s="9" t="inlineStr">
-        <is>
-          <t>Operator screens</t>
-        </is>
-      </c>
-      <c r="G38" s="10" t="inlineStr">
-        <is>
-          <t>3.9</t>
-        </is>
-      </c>
-      <c r="H38" s="10" t="inlineStr">
-        <is>
-          <t>S4</t>
-        </is>
-      </c>
-      <c r="I38" s="10" t="inlineStr">
-        <is>
-          <t>S3</t>
-        </is>
-      </c>
-      <c r="J38" s="10" t="inlineStr">
-        <is>
-          <t>S2</t>
         </is>
       </c>
     </row>
@@ -5174,22 +3800,12 @@
       </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
-          <t>S4</t>
-        </is>
-      </c>
-      <c r="I39" s="7" t="inlineStr">
-        <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="J39" s="7" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
     </row>
     <row r="40">
-      <c r="A40" s="10" t="inlineStr">
+      <c r="A40" s="11" t="inlineStr">
         <is>
           <t>36</t>
         </is>
@@ -5219,24 +3835,14 @@
           <t>Application services</t>
         </is>
       </c>
-      <c r="G40" s="10" t="inlineStr">
+      <c r="G40" s="11" t="inlineStr">
         <is>
           <t>1.4</t>
         </is>
       </c>
-      <c r="H40" s="10" t="inlineStr">
-        <is>
-          <t>S4</t>
-        </is>
-      </c>
-      <c r="I40" s="10" t="inlineStr">
+      <c r="H40" s="11" t="inlineStr">
         <is>
           <t>S3</t>
-        </is>
-      </c>
-      <c r="J40" s="10" t="inlineStr">
-        <is>
-          <t>S2</t>
         </is>
       </c>
     </row>
@@ -5278,22 +3884,12 @@
       </c>
       <c r="H41" s="7" t="inlineStr">
         <is>
-          <t>S4</t>
-        </is>
-      </c>
-      <c r="I41" s="7" t="inlineStr">
-        <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="J41" s="7" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
     </row>
     <row r="42">
-      <c r="A42" s="10" t="inlineStr">
+      <c r="A42" s="11" t="inlineStr">
         <is>
           <t>38</t>
         </is>
@@ -5323,24 +3919,14 @@
           <t>Live data and machine interface</t>
         </is>
       </c>
-      <c r="G42" s="10" t="inlineStr">
+      <c r="G42" s="11" t="inlineStr">
         <is>
           <t>3.5</t>
         </is>
       </c>
-      <c r="H42" s="10" t="inlineStr">
-        <is>
-          <t>S4</t>
-        </is>
-      </c>
-      <c r="I42" s="10" t="inlineStr">
+      <c r="H42" s="11" t="inlineStr">
         <is>
           <t>S3</t>
-        </is>
-      </c>
-      <c r="J42" s="10" t="inlineStr">
-        <is>
-          <t>S2</t>
         </is>
       </c>
     </row>
@@ -5382,22 +3968,12 @@
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
-          <t>S4</t>
-        </is>
-      </c>
-      <c r="I43" s="7" t="inlineStr">
-        <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="J43" s="7" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
     </row>
     <row r="44">
-      <c r="A44" s="10" t="inlineStr">
+      <c r="A44" s="11" t="inlineStr">
         <is>
           <t>40</t>
         </is>
@@ -5427,22 +4003,12 @@
           <t>Live data and machine interface</t>
         </is>
       </c>
-      <c r="G44" s="10" t="inlineStr">
+      <c r="G44" s="11" t="inlineStr">
         <is>
           <t>1.4</t>
         </is>
       </c>
-      <c r="H44" s="10" t="inlineStr">
-        <is>
-          <t>S5</t>
-        </is>
-      </c>
-      <c r="I44" s="10" t="inlineStr">
-        <is>
-          <t>S3</t>
-        </is>
-      </c>
-      <c r="J44" s="10" t="inlineStr">
+      <c r="H44" s="11" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
@@ -5486,22 +4052,12 @@
       </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
-          <t>S4</t>
-        </is>
-      </c>
-      <c r="I45" s="7" t="inlineStr">
-        <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="J45" s="7" t="inlineStr">
-        <is>
-          <t>S3</t>
-        </is>
-      </c>
     </row>
     <row r="46">
-      <c r="A46" s="10" t="inlineStr">
+      <c r="A46" s="11" t="inlineStr">
         <is>
           <t>42</t>
         </is>
@@ -5531,22 +4087,12 @@
           <t>Application services</t>
         </is>
       </c>
-      <c r="G46" s="10" t="inlineStr">
+      <c r="G46" s="11" t="inlineStr">
         <is>
           <t>2.2</t>
         </is>
       </c>
-      <c r="H46" s="10" t="inlineStr">
-        <is>
-          <t>S5</t>
-        </is>
-      </c>
-      <c r="I46" s="10" t="inlineStr">
-        <is>
-          <t>S3</t>
-        </is>
-      </c>
-      <c r="J46" s="10" t="inlineStr">
+      <c r="H46" s="11" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
@@ -5590,22 +4136,12 @@
       </c>
       <c r="H47" s="7" t="inlineStr">
         <is>
-          <t>S5</t>
-        </is>
-      </c>
-      <c r="I47" s="7" t="inlineStr">
-        <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="J47" s="7" t="inlineStr">
-        <is>
-          <t>S3</t>
-        </is>
-      </c>
     </row>
     <row r="48">
-      <c r="A48" s="10" t="inlineStr">
+      <c r="A48" s="11" t="inlineStr">
         <is>
           <t>44</t>
         </is>
@@ -5635,22 +4171,12 @@
           <t>Live data and machine interface</t>
         </is>
       </c>
-      <c r="G48" s="10" t="inlineStr">
+      <c r="G48" s="11" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="H48" s="10" t="inlineStr">
-        <is>
-          <t>S5</t>
-        </is>
-      </c>
-      <c r="I48" s="10" t="inlineStr">
-        <is>
-          <t>S3</t>
-        </is>
-      </c>
-      <c r="J48" s="10" t="inlineStr">
+      <c r="H48" s="11" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
@@ -5694,22 +4220,12 @@
       </c>
       <c r="H49" s="7" t="inlineStr">
         <is>
-          <t>S5</t>
-        </is>
-      </c>
-      <c r="I49" s="7" t="inlineStr">
-        <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="J49" s="7" t="inlineStr">
-        <is>
-          <t>S3</t>
-        </is>
-      </c>
     </row>
     <row r="50">
-      <c r="A50" s="10" t="inlineStr">
+      <c r="A50" s="11" t="inlineStr">
         <is>
           <t>46</t>
         </is>
@@ -5739,24 +4255,14 @@
           <t>Operator screens</t>
         </is>
       </c>
-      <c r="G50" s="10" t="inlineStr">
+      <c r="G50" s="11" t="inlineStr">
         <is>
           <t>2.6</t>
         </is>
       </c>
-      <c r="H50" s="10" t="inlineStr">
-        <is>
-          <t>S5</t>
-        </is>
-      </c>
-      <c r="I50" s="10" t="inlineStr">
+      <c r="H50" s="11" t="inlineStr">
         <is>
           <t>S4</t>
-        </is>
-      </c>
-      <c r="J50" s="10" t="inlineStr">
-        <is>
-          <t>S3</t>
         </is>
       </c>
     </row>
@@ -5798,22 +4304,12 @@
       </c>
       <c r="H51" s="7" t="inlineStr">
         <is>
-          <t>S5</t>
-        </is>
-      </c>
-      <c r="I51" s="7" t="inlineStr">
-        <is>
           <t>S4</t>
         </is>
       </c>
-      <c r="J51" s="7" t="inlineStr">
-        <is>
-          <t>S3</t>
-        </is>
-      </c>
     </row>
     <row r="52">
-      <c r="A52" s="10" t="inlineStr">
+      <c r="A52" s="11" t="inlineStr">
         <is>
           <t>48</t>
         </is>
@@ -5843,24 +4339,14 @@
           <t>Operator screens</t>
         </is>
       </c>
-      <c r="G52" s="10" t="inlineStr">
+      <c r="G52" s="11" t="inlineStr">
         <is>
           <t>1.6</t>
         </is>
       </c>
-      <c r="H52" s="10" t="inlineStr">
-        <is>
-          <t>S5</t>
-        </is>
-      </c>
-      <c r="I52" s="10" t="inlineStr">
+      <c r="H52" s="11" t="inlineStr">
         <is>
           <t>S4</t>
-        </is>
-      </c>
-      <c r="J52" s="10" t="inlineStr">
-        <is>
-          <t>S3</t>
         </is>
       </c>
     </row>
@@ -5902,22 +4388,12 @@
       </c>
       <c r="H53" s="7" t="inlineStr">
         <is>
-          <t>S5</t>
-        </is>
-      </c>
-      <c r="I53" s="7" t="inlineStr">
-        <is>
           <t>S4</t>
         </is>
       </c>
-      <c r="J53" s="7" t="inlineStr">
-        <is>
-          <t>S3</t>
-        </is>
-      </c>
     </row>
     <row r="54">
-      <c r="A54" s="10" t="inlineStr">
+      <c r="A54" s="11" t="inlineStr">
         <is>
           <t>50</t>
         </is>
@@ -5947,24 +4423,14 @@
           <t>Application services</t>
         </is>
       </c>
-      <c r="G54" s="10" t="inlineStr">
+      <c r="G54" s="11" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="H54" s="10" t="inlineStr">
-        <is>
-          <t>S5</t>
-        </is>
-      </c>
-      <c r="I54" s="10" t="inlineStr">
+      <c r="H54" s="11" t="inlineStr">
         <is>
           <t>S4</t>
-        </is>
-      </c>
-      <c r="J54" s="10" t="inlineStr">
-        <is>
-          <t>S3</t>
         </is>
       </c>
     </row>
@@ -6006,22 +4472,12 @@
       </c>
       <c r="H55" s="7" t="inlineStr">
         <is>
-          <t>S5</t>
-        </is>
-      </c>
-      <c r="I55" s="7" t="inlineStr">
-        <is>
           <t>S4</t>
         </is>
       </c>
-      <c r="J55" s="7" t="inlineStr">
-        <is>
-          <t>S3</t>
-        </is>
-      </c>
     </row>
     <row r="56">
-      <c r="A56" s="10" t="inlineStr">
+      <c r="A56" s="11" t="inlineStr">
         <is>
           <t>52</t>
         </is>
@@ -6051,24 +4507,14 @@
           <t>Operator screens</t>
         </is>
       </c>
-      <c r="G56" s="10" t="inlineStr">
+      <c r="G56" s="11" t="inlineStr">
         <is>
           <t>1.6</t>
         </is>
       </c>
-      <c r="H56" s="10" t="inlineStr">
-        <is>
-          <t>S5</t>
-        </is>
-      </c>
-      <c r="I56" s="10" t="inlineStr">
+      <c r="H56" s="11" t="inlineStr">
         <is>
           <t>S4</t>
-        </is>
-      </c>
-      <c r="J56" s="10" t="inlineStr">
-        <is>
-          <t>S3</t>
         </is>
       </c>
     </row>
@@ -6110,22 +4556,12 @@
       </c>
       <c r="H57" s="7" t="inlineStr">
         <is>
-          <t>S6</t>
-        </is>
-      </c>
-      <c r="I57" s="7" t="inlineStr">
-        <is>
           <t>S4</t>
         </is>
       </c>
-      <c r="J57" s="7" t="inlineStr">
-        <is>
-          <t>S3</t>
-        </is>
-      </c>
     </row>
     <row r="58">
-      <c r="A58" s="10" t="inlineStr">
+      <c r="A58" s="11" t="inlineStr">
         <is>
           <t>54</t>
         </is>
@@ -6155,24 +4591,14 @@
           <t>Operator screens</t>
         </is>
       </c>
-      <c r="G58" s="10" t="inlineStr">
+      <c r="G58" s="11" t="inlineStr">
         <is>
           <t>2.2</t>
         </is>
       </c>
-      <c r="H58" s="10" t="inlineStr">
-        <is>
-          <t>S6</t>
-        </is>
-      </c>
-      <c r="I58" s="10" t="inlineStr">
+      <c r="H58" s="11" t="inlineStr">
         <is>
           <t>S4</t>
-        </is>
-      </c>
-      <c r="J58" s="10" t="inlineStr">
-        <is>
-          <t>S3</t>
         </is>
       </c>
     </row>
@@ -6214,22 +4640,12 @@
       </c>
       <c r="H59" s="7" t="inlineStr">
         <is>
-          <t>S6</t>
-        </is>
-      </c>
-      <c r="I59" s="7" t="inlineStr">
-        <is>
           <t>S4</t>
         </is>
       </c>
-      <c r="J59" s="7" t="inlineStr">
-        <is>
-          <t>S3</t>
-        </is>
-      </c>
     </row>
     <row r="60">
-      <c r="A60" s="10" t="inlineStr">
+      <c r="A60" s="11" t="inlineStr">
         <is>
           <t>56</t>
         </is>
@@ -6259,24 +4675,14 @@
           <t>Operator screens</t>
         </is>
       </c>
-      <c r="G60" s="10" t="inlineStr">
+      <c r="G60" s="11" t="inlineStr">
         <is>
           <t>1.9</t>
         </is>
       </c>
-      <c r="H60" s="10" t="inlineStr">
-        <is>
-          <t>S6</t>
-        </is>
-      </c>
-      <c r="I60" s="10" t="inlineStr">
+      <c r="H60" s="11" t="inlineStr">
         <is>
           <t>S4</t>
-        </is>
-      </c>
-      <c r="J60" s="10" t="inlineStr">
-        <is>
-          <t>S3</t>
         </is>
       </c>
     </row>
@@ -6318,22 +4724,12 @@
       </c>
       <c r="H61" s="7" t="inlineStr">
         <is>
-          <t>S6</t>
-        </is>
-      </c>
-      <c r="I61" s="7" t="inlineStr">
-        <is>
           <t>S4</t>
         </is>
       </c>
-      <c r="J61" s="7" t="inlineStr">
-        <is>
-          <t>S3</t>
-        </is>
-      </c>
     </row>
     <row r="62">
-      <c r="A62" s="10" t="inlineStr">
+      <c r="A62" s="11" t="inlineStr">
         <is>
           <t>58</t>
         </is>
@@ -6363,24 +4759,14 @@
           <t>Application services</t>
         </is>
       </c>
-      <c r="G62" s="10" t="inlineStr">
+      <c r="G62" s="11" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="H62" s="10" t="inlineStr">
-        <is>
-          <t>S6</t>
-        </is>
-      </c>
-      <c r="I62" s="10" t="inlineStr">
+      <c r="H62" s="11" t="inlineStr">
         <is>
           <t>S4</t>
-        </is>
-      </c>
-      <c r="J62" s="10" t="inlineStr">
-        <is>
-          <t>S3</t>
         </is>
       </c>
     </row>
@@ -6422,22 +4808,12 @@
       </c>
       <c r="H63" s="7" t="inlineStr">
         <is>
-          <t>S6</t>
-        </is>
-      </c>
-      <c r="I63" s="7" t="inlineStr">
-        <is>
           <t>S4</t>
         </is>
       </c>
-      <c r="J63" s="7" t="inlineStr">
-        <is>
-          <t>S3</t>
-        </is>
-      </c>
     </row>
     <row r="64">
-      <c r="A64" s="10" t="inlineStr">
+      <c r="A64" s="11" t="inlineStr">
         <is>
           <t>60</t>
         </is>
@@ -6467,24 +4843,14 @@
           <t>Application services</t>
         </is>
       </c>
-      <c r="G64" s="10" t="inlineStr">
+      <c r="G64" s="11" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="H64" s="10" t="inlineStr">
-        <is>
-          <t>S6</t>
-        </is>
-      </c>
-      <c r="I64" s="10" t="inlineStr">
+      <c r="H64" s="11" t="inlineStr">
         <is>
           <t>S4</t>
-        </is>
-      </c>
-      <c r="J64" s="10" t="inlineStr">
-        <is>
-          <t>S3</t>
         </is>
       </c>
     </row>
@@ -6526,22 +4892,12 @@
       </c>
       <c r="H65" s="7" t="inlineStr">
         <is>
-          <t>S6</t>
-        </is>
-      </c>
-      <c r="I65" s="7" t="inlineStr">
-        <is>
           <t>S4</t>
         </is>
       </c>
-      <c r="J65" s="7" t="inlineStr">
-        <is>
-          <t>S3</t>
-        </is>
-      </c>
     </row>
     <row r="66">
-      <c r="A66" s="10" t="inlineStr">
+      <c r="A66" s="11" t="inlineStr">
         <is>
           <t>62</t>
         </is>
@@ -6571,24 +4927,14 @@
           <t>Data</t>
         </is>
       </c>
-      <c r="G66" s="10" t="inlineStr">
+      <c r="G66" s="11" t="inlineStr">
         <is>
           <t>1.6</t>
         </is>
       </c>
-      <c r="H66" s="10" t="inlineStr">
-        <is>
-          <t>S6</t>
-        </is>
-      </c>
-      <c r="I66" s="10" t="inlineStr">
+      <c r="H66" s="11" t="inlineStr">
         <is>
           <t>S4</t>
-        </is>
-      </c>
-      <c r="J66" s="10" t="inlineStr">
-        <is>
-          <t>S3</t>
         </is>
       </c>
     </row>
@@ -6630,22 +4976,12 @@
       </c>
       <c r="H67" s="7" t="inlineStr">
         <is>
-          <t>S6</t>
-        </is>
-      </c>
-      <c r="I67" s="7" t="inlineStr">
-        <is>
           <t>S4</t>
         </is>
       </c>
-      <c r="J67" s="7" t="inlineStr">
-        <is>
-          <t>S3</t>
-        </is>
-      </c>
     </row>
     <row r="68">
-      <c r="A68" s="10" t="inlineStr">
+      <c r="A68" s="11" t="inlineStr">
         <is>
           <t>64</t>
         </is>
@@ -6675,22 +5011,12 @@
           <t>Operator screens</t>
         </is>
       </c>
-      <c r="G68" s="10" t="inlineStr">
+      <c r="G68" s="11" t="inlineStr">
         <is>
           <t>1.6</t>
         </is>
       </c>
-      <c r="H68" s="10" t="inlineStr">
-        <is>
-          <t>S6</t>
-        </is>
-      </c>
-      <c r="I68" s="10" t="inlineStr">
-        <is>
-          <t>S4</t>
-        </is>
-      </c>
-      <c r="J68" s="10" t="inlineStr">
+      <c r="H68" s="11" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
@@ -6734,22 +5060,12 @@
       </c>
       <c r="H69" s="7" t="inlineStr">
         <is>
-          <t>S6</t>
-        </is>
-      </c>
-      <c r="I69" s="7" t="inlineStr">
-        <is>
           <t>S4</t>
         </is>
       </c>
-      <c r="J69" s="7" t="inlineStr">
-        <is>
-          <t>S4</t>
-        </is>
-      </c>
     </row>
     <row r="70">
-      <c r="A70" s="10" t="inlineStr">
+      <c r="A70" s="11" t="inlineStr">
         <is>
           <t>66</t>
         </is>
@@ -6779,24 +5095,14 @@
           <t>Operator screens</t>
         </is>
       </c>
-      <c r="G70" s="10" t="inlineStr">
+      <c r="G70" s="11" t="inlineStr">
         <is>
           <t>1.6</t>
         </is>
       </c>
-      <c r="H70" s="10" t="inlineStr">
-        <is>
-          <t>S7</t>
-        </is>
-      </c>
-      <c r="I70" s="10" t="inlineStr">
+      <c r="H70" s="11" t="inlineStr">
         <is>
           <t>S5</t>
-        </is>
-      </c>
-      <c r="J70" s="10" t="inlineStr">
-        <is>
-          <t>S4</t>
         </is>
       </c>
     </row>
@@ -6838,22 +5144,12 @@
       </c>
       <c r="H71" s="7" t="inlineStr">
         <is>
-          <t>S7</t>
-        </is>
-      </c>
-      <c r="I71" s="7" t="inlineStr">
-        <is>
           <t>S5</t>
         </is>
       </c>
-      <c r="J71" s="7" t="inlineStr">
-        <is>
-          <t>S4</t>
-        </is>
-      </c>
     </row>
     <row r="72">
-      <c r="A72" s="10" t="inlineStr">
+      <c r="A72" s="11" t="inlineStr">
         <is>
           <t>68</t>
         </is>
@@ -6883,24 +5179,14 @@
           <t>Application services</t>
         </is>
       </c>
-      <c r="G72" s="10" t="inlineStr">
+      <c r="G72" s="11" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="H72" s="10" t="inlineStr">
-        <is>
-          <t>S7</t>
-        </is>
-      </c>
-      <c r="I72" s="10" t="inlineStr">
+      <c r="H72" s="11" t="inlineStr">
         <is>
           <t>S5</t>
-        </is>
-      </c>
-      <c r="J72" s="10" t="inlineStr">
-        <is>
-          <t>S4</t>
         </is>
       </c>
     </row>
@@ -6942,22 +5228,12 @@
       </c>
       <c r="H73" s="7" t="inlineStr">
         <is>
-          <t>S7</t>
-        </is>
-      </c>
-      <c r="I73" s="7" t="inlineStr">
-        <is>
           <t>S5</t>
         </is>
       </c>
-      <c r="J73" s="7" t="inlineStr">
-        <is>
-          <t>S4</t>
-        </is>
-      </c>
     </row>
     <row r="74">
-      <c r="A74" s="10" t="inlineStr">
+      <c r="A74" s="11" t="inlineStr">
         <is>
           <t>70</t>
         </is>
@@ -6987,24 +5263,14 @@
           <t>Live data and machine interface</t>
         </is>
       </c>
-      <c r="G74" s="10" t="inlineStr">
+      <c r="G74" s="11" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="H74" s="10" t="inlineStr">
-        <is>
-          <t>S7</t>
-        </is>
-      </c>
-      <c r="I74" s="10" t="inlineStr">
+      <c r="H74" s="11" t="inlineStr">
         <is>
           <t>S5</t>
-        </is>
-      </c>
-      <c r="J74" s="10" t="inlineStr">
-        <is>
-          <t>S4</t>
         </is>
       </c>
     </row>
@@ -7046,22 +5312,12 @@
       </c>
       <c r="H75" s="7" t="inlineStr">
         <is>
-          <t>S7</t>
-        </is>
-      </c>
-      <c r="I75" s="7" t="inlineStr">
-        <is>
           <t>S5</t>
         </is>
       </c>
-      <c r="J75" s="7" t="inlineStr">
-        <is>
-          <t>S4</t>
-        </is>
-      </c>
     </row>
     <row r="76">
-      <c r="A76" s="10" t="inlineStr">
+      <c r="A76" s="11" t="inlineStr">
         <is>
           <t>72</t>
         </is>
@@ -7091,24 +5347,14 @@
           <t>Operator screens</t>
         </is>
       </c>
-      <c r="G76" s="10" t="inlineStr">
+      <c r="G76" s="11" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="H76" s="10" t="inlineStr">
-        <is>
-          <t>S7</t>
-        </is>
-      </c>
-      <c r="I76" s="10" t="inlineStr">
+      <c r="H76" s="11" t="inlineStr">
         <is>
           <t>S5</t>
-        </is>
-      </c>
-      <c r="J76" s="10" t="inlineStr">
-        <is>
-          <t>S4</t>
         </is>
       </c>
     </row>
@@ -7150,22 +5396,12 @@
       </c>
       <c r="H77" s="7" t="inlineStr">
         <is>
-          <t>S7</t>
-        </is>
-      </c>
-      <c r="I77" s="7" t="inlineStr">
-        <is>
           <t>S5</t>
         </is>
       </c>
-      <c r="J77" s="7" t="inlineStr">
-        <is>
-          <t>S4</t>
-        </is>
-      </c>
     </row>
     <row r="78">
-      <c r="A78" s="10" t="inlineStr">
+      <c r="A78" s="11" t="inlineStr">
         <is>
           <t>74</t>
         </is>
@@ -7195,24 +5431,14 @@
           <t>Application services</t>
         </is>
       </c>
-      <c r="G78" s="10" t="inlineStr">
+      <c r="G78" s="11" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="H78" s="10" t="inlineStr">
-        <is>
-          <t>S7</t>
-        </is>
-      </c>
-      <c r="I78" s="10" t="inlineStr">
+      <c r="H78" s="11" t="inlineStr">
         <is>
           <t>S5</t>
-        </is>
-      </c>
-      <c r="J78" s="10" t="inlineStr">
-        <is>
-          <t>S4</t>
         </is>
       </c>
     </row>
@@ -7254,22 +5480,12 @@
       </c>
       <c r="H79" s="7" t="inlineStr">
         <is>
-          <t>S7</t>
-        </is>
-      </c>
-      <c r="I79" s="7" t="inlineStr">
-        <is>
           <t>S5</t>
         </is>
       </c>
-      <c r="J79" s="7" t="inlineStr">
-        <is>
-          <t>S4</t>
-        </is>
-      </c>
     </row>
     <row r="80">
-      <c r="A80" s="10" t="inlineStr">
+      <c r="A80" s="11" t="inlineStr">
         <is>
           <t>76</t>
         </is>
@@ -7299,24 +5515,14 @@
           <t>Live data and machine interface</t>
         </is>
       </c>
-      <c r="G80" s="10" t="inlineStr">
+      <c r="G80" s="11" t="inlineStr">
         <is>
           <t>0.4</t>
         </is>
       </c>
-      <c r="H80" s="10" t="inlineStr">
-        <is>
-          <t>S7</t>
-        </is>
-      </c>
-      <c r="I80" s="10" t="inlineStr">
+      <c r="H80" s="11" t="inlineStr">
         <is>
           <t>S5</t>
-        </is>
-      </c>
-      <c r="J80" s="10" t="inlineStr">
-        <is>
-          <t>S4</t>
         </is>
       </c>
     </row>
@@ -7358,22 +5564,12 @@
       </c>
       <c r="H81" s="7" t="inlineStr">
         <is>
-          <t>S7</t>
-        </is>
-      </c>
-      <c r="I81" s="7" t="inlineStr">
-        <is>
           <t>S5</t>
         </is>
       </c>
-      <c r="J81" s="7" t="inlineStr">
-        <is>
-          <t>S4</t>
-        </is>
-      </c>
     </row>
     <row r="82">
-      <c r="A82" s="10" t="inlineStr">
+      <c r="A82" s="11" t="inlineStr">
         <is>
           <t>78</t>
         </is>
@@ -7403,24 +5599,14 @@
           <t>Operator screens</t>
         </is>
       </c>
-      <c r="G82" s="10" t="inlineStr">
+      <c r="G82" s="11" t="inlineStr">
         <is>
           <t>1.9</t>
         </is>
       </c>
-      <c r="H82" s="10" t="inlineStr">
-        <is>
-          <t>S8</t>
-        </is>
-      </c>
-      <c r="I82" s="10" t="inlineStr">
+      <c r="H82" s="11" t="inlineStr">
         <is>
           <t>S5</t>
-        </is>
-      </c>
-      <c r="J82" s="10" t="inlineStr">
-        <is>
-          <t>S4</t>
         </is>
       </c>
     </row>
@@ -7462,22 +5648,12 @@
       </c>
       <c r="H83" s="7" t="inlineStr">
         <is>
-          <t>S8</t>
-        </is>
-      </c>
-      <c r="I83" s="7" t="inlineStr">
-        <is>
           <t>S5</t>
         </is>
       </c>
-      <c r="J83" s="7" t="inlineStr">
-        <is>
-          <t>S4</t>
-        </is>
-      </c>
     </row>
     <row r="84">
-      <c r="A84" s="10" t="inlineStr">
+      <c r="A84" s="11" t="inlineStr">
         <is>
           <t>80</t>
         </is>
@@ -7507,24 +5683,14 @@
           <t>Operator screens</t>
         </is>
       </c>
-      <c r="G84" s="10" t="inlineStr">
+      <c r="G84" s="11" t="inlineStr">
         <is>
           <t>3.2</t>
         </is>
       </c>
-      <c r="H84" s="10" t="inlineStr">
-        <is>
-          <t>S8</t>
-        </is>
-      </c>
-      <c r="I84" s="10" t="inlineStr">
+      <c r="H84" s="11" t="inlineStr">
         <is>
           <t>S5</t>
-        </is>
-      </c>
-      <c r="J84" s="10" t="inlineStr">
-        <is>
-          <t>S4</t>
         </is>
       </c>
     </row>
@@ -7566,22 +5732,12 @@
       </c>
       <c r="H85" s="7" t="inlineStr">
         <is>
-          <t>S8</t>
-        </is>
-      </c>
-      <c r="I85" s="7" t="inlineStr">
-        <is>
           <t>S5</t>
         </is>
       </c>
-      <c r="J85" s="7" t="inlineStr">
-        <is>
-          <t>S4</t>
-        </is>
-      </c>
     </row>
     <row r="86">
-      <c r="A86" s="10" t="inlineStr">
+      <c r="A86" s="11" t="inlineStr">
         <is>
           <t>82</t>
         </is>
@@ -7611,24 +5767,14 @@
           <t>Application services</t>
         </is>
       </c>
-      <c r="G86" s="10" t="inlineStr">
+      <c r="G86" s="11" t="inlineStr">
         <is>
           <t>2.1</t>
         </is>
       </c>
-      <c r="H86" s="10" t="inlineStr">
-        <is>
-          <t>S8</t>
-        </is>
-      </c>
-      <c r="I86" s="10" t="inlineStr">
+      <c r="H86" s="11" t="inlineStr">
         <is>
           <t>S5</t>
-        </is>
-      </c>
-      <c r="J86" s="10" t="inlineStr">
-        <is>
-          <t>S4</t>
         </is>
       </c>
     </row>
@@ -7670,22 +5816,12 @@
       </c>
       <c r="H87" s="7" t="inlineStr">
         <is>
-          <t>S8</t>
-        </is>
-      </c>
-      <c r="I87" s="7" t="inlineStr">
-        <is>
           <t>S5</t>
         </is>
       </c>
-      <c r="J87" s="7" t="inlineStr">
-        <is>
-          <t>S4</t>
-        </is>
-      </c>
     </row>
     <row r="88">
-      <c r="A88" s="10" t="inlineStr">
+      <c r="A88" s="11" t="inlineStr">
         <is>
           <t>84</t>
         </is>
@@ -7715,24 +5851,14 @@
           <t>Live data and machine interface</t>
         </is>
       </c>
-      <c r="G88" s="10" t="inlineStr">
+      <c r="G88" s="11" t="inlineStr">
         <is>
           <t>0.6</t>
         </is>
       </c>
-      <c r="H88" s="10" t="inlineStr">
-        <is>
-          <t>S8</t>
-        </is>
-      </c>
-      <c r="I88" s="10" t="inlineStr">
+      <c r="H88" s="11" t="inlineStr">
         <is>
           <t>S5</t>
-        </is>
-      </c>
-      <c r="J88" s="10" t="inlineStr">
-        <is>
-          <t>S4</t>
         </is>
       </c>
     </row>
@@ -7774,22 +5900,12 @@
       </c>
       <c r="H89" s="7" t="inlineStr">
         <is>
-          <t>S8</t>
-        </is>
-      </c>
-      <c r="I89" s="7" t="inlineStr">
-        <is>
           <t>S5</t>
         </is>
       </c>
-      <c r="J89" s="7" t="inlineStr">
-        <is>
-          <t>S4</t>
-        </is>
-      </c>
     </row>
     <row r="90">
-      <c r="A90" s="10" t="inlineStr">
+      <c r="A90" s="11" t="inlineStr">
         <is>
           <t>86</t>
         </is>
@@ -7819,24 +5935,14 @@
           <t>Application services</t>
         </is>
       </c>
-      <c r="G90" s="10" t="inlineStr">
+      <c r="G90" s="11" t="inlineStr">
         <is>
           <t>1.8</t>
         </is>
       </c>
-      <c r="H90" s="10" t="inlineStr">
-        <is>
-          <t>S8</t>
-        </is>
-      </c>
-      <c r="I90" s="10" t="inlineStr">
+      <c r="H90" s="11" t="inlineStr">
         <is>
           <t>S5</t>
-        </is>
-      </c>
-      <c r="J90" s="10" t="inlineStr">
-        <is>
-          <t>S4</t>
         </is>
       </c>
     </row>
@@ -7878,22 +5984,12 @@
       </c>
       <c r="H91" s="7" t="inlineStr">
         <is>
-          <t>S8</t>
-        </is>
-      </c>
-      <c r="I91" s="7" t="inlineStr">
-        <is>
           <t>S6</t>
         </is>
       </c>
-      <c r="J91" s="7" t="inlineStr">
-        <is>
-          <t>S4</t>
-        </is>
-      </c>
     </row>
     <row r="92">
-      <c r="A92" s="10" t="inlineStr">
+      <c r="A92" s="11" t="inlineStr">
         <is>
           <t>88</t>
         </is>
@@ -7923,24 +6019,14 @@
           <t>Live data and machine interface</t>
         </is>
       </c>
-      <c r="G92" s="10" t="inlineStr">
+      <c r="G92" s="11" t="inlineStr">
         <is>
           <t>0.8</t>
         </is>
       </c>
-      <c r="H92" s="10" t="inlineStr">
-        <is>
-          <t>S8</t>
-        </is>
-      </c>
-      <c r="I92" s="10" t="inlineStr">
+      <c r="H92" s="11" t="inlineStr">
         <is>
           <t>S6</t>
-        </is>
-      </c>
-      <c r="J92" s="10" t="inlineStr">
-        <is>
-          <t>S4</t>
         </is>
       </c>
     </row>
@@ -7982,22 +6068,12 @@
       </c>
       <c r="H93" s="7" t="inlineStr">
         <is>
-          <t>S8</t>
-        </is>
-      </c>
-      <c r="I93" s="7" t="inlineStr">
-        <is>
           <t>S6</t>
         </is>
       </c>
-      <c r="J93" s="7" t="inlineStr">
-        <is>
-          <t>S4</t>
-        </is>
-      </c>
     </row>
     <row r="94">
-      <c r="A94" s="10" t="inlineStr">
+      <c r="A94" s="11" t="inlineStr">
         <is>
           <t>90</t>
         </is>
@@ -8027,24 +6103,14 @@
           <t>Operator screens + Application services + Live data and machine interface</t>
         </is>
       </c>
-      <c r="G94" s="10" t="inlineStr">
+      <c r="G94" s="11" t="inlineStr">
         <is>
           <t>1.6</t>
         </is>
       </c>
-      <c r="H94" s="10" t="inlineStr">
-        <is>
-          <t>S8</t>
-        </is>
-      </c>
-      <c r="I94" s="10" t="inlineStr">
+      <c r="H94" s="11" t="inlineStr">
         <is>
           <t>S6</t>
-        </is>
-      </c>
-      <c r="J94" s="10" t="inlineStr">
-        <is>
-          <t>S4</t>
         </is>
       </c>
     </row>
@@ -8086,22 +6152,12 @@
       </c>
       <c r="H95" s="7" t="inlineStr">
         <is>
-          <t>S9</t>
-        </is>
-      </c>
-      <c r="I95" s="7" t="inlineStr">
-        <is>
           <t>S6</t>
         </is>
       </c>
-      <c r="J95" s="7" t="inlineStr">
-        <is>
-          <t>S5</t>
-        </is>
-      </c>
     </row>
     <row r="96">
-      <c r="A96" s="10" t="inlineStr">
+      <c r="A96" s="11" t="inlineStr">
         <is>
           <t>92</t>
         </is>
@@ -8131,24 +6187,14 @@
           <t>Operator screens + Application services</t>
         </is>
       </c>
-      <c r="G96" s="10" t="inlineStr">
+      <c r="G96" s="11" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="H96" s="10" t="inlineStr">
-        <is>
-          <t>S9</t>
-        </is>
-      </c>
-      <c r="I96" s="10" t="inlineStr">
+      <c r="H96" s="11" t="inlineStr">
         <is>
           <t>S6</t>
-        </is>
-      </c>
-      <c r="J96" s="10" t="inlineStr">
-        <is>
-          <t>S5</t>
         </is>
       </c>
     </row>
@@ -8190,22 +6236,12 @@
       </c>
       <c r="H97" s="7" t="inlineStr">
         <is>
-          <t>S9</t>
-        </is>
-      </c>
-      <c r="I97" s="7" t="inlineStr">
-        <is>
           <t>S6</t>
         </is>
       </c>
-      <c r="J97" s="7" t="inlineStr">
-        <is>
-          <t>S5</t>
-        </is>
-      </c>
     </row>
     <row r="98">
-      <c r="A98" s="10" t="inlineStr">
+      <c r="A98" s="11" t="inlineStr">
         <is>
           <t>94</t>
         </is>
@@ -8235,24 +6271,14 @@
           <t>Operator screens + Application services</t>
         </is>
       </c>
-      <c r="G98" s="10" t="inlineStr">
+      <c r="G98" s="11" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="H98" s="10" t="inlineStr">
-        <is>
-          <t>S9</t>
-        </is>
-      </c>
-      <c r="I98" s="10" t="inlineStr">
+      <c r="H98" s="11" t="inlineStr">
         <is>
           <t>S6</t>
-        </is>
-      </c>
-      <c r="J98" s="10" t="inlineStr">
-        <is>
-          <t>S5</t>
         </is>
       </c>
     </row>
@@ -8294,22 +6320,12 @@
       </c>
       <c r="H99" s="7" t="inlineStr">
         <is>
-          <t>S9</t>
-        </is>
-      </c>
-      <c r="I99" s="7" t="inlineStr">
-        <is>
           <t>S6</t>
         </is>
       </c>
-      <c r="J99" s="7" t="inlineStr">
-        <is>
-          <t>S5</t>
-        </is>
-      </c>
     </row>
     <row r="100">
-      <c r="A100" s="10" t="inlineStr">
+      <c r="A100" s="11" t="inlineStr">
         <is>
           <t>96</t>
         </is>
@@ -8339,24 +6355,14 @@
           <t>Operator screens</t>
         </is>
       </c>
-      <c r="G100" s="10" t="inlineStr">
+      <c r="G100" s="11" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="H100" s="10" t="inlineStr">
-        <is>
-          <t>S9</t>
-        </is>
-      </c>
-      <c r="I100" s="10" t="inlineStr">
+      <c r="H100" s="11" t="inlineStr">
         <is>
           <t>S6</t>
-        </is>
-      </c>
-      <c r="J100" s="10" t="inlineStr">
-        <is>
-          <t>S5</t>
         </is>
       </c>
     </row>
@@ -8398,22 +6404,12 @@
       </c>
       <c r="H101" s="7" t="inlineStr">
         <is>
-          <t>S9</t>
-        </is>
-      </c>
-      <c r="I101" s="7" t="inlineStr">
-        <is>
           <t>S6</t>
         </is>
       </c>
-      <c r="J101" s="7" t="inlineStr">
-        <is>
-          <t>S5</t>
-        </is>
-      </c>
     </row>
     <row r="102">
-      <c r="A102" s="10" t="inlineStr">
+      <c r="A102" s="11" t="inlineStr">
         <is>
           <t>98</t>
         </is>
@@ -8443,24 +6439,14 @@
           <t>Operator screens</t>
         </is>
       </c>
-      <c r="G102" s="10" t="inlineStr">
+      <c r="G102" s="11" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="H102" s="10" t="inlineStr">
-        <is>
-          <t>S9</t>
-        </is>
-      </c>
-      <c r="I102" s="10" t="inlineStr">
+      <c r="H102" s="11" t="inlineStr">
         <is>
           <t>S6</t>
-        </is>
-      </c>
-      <c r="J102" s="10" t="inlineStr">
-        <is>
-          <t>S5</t>
         </is>
       </c>
     </row>
@@ -8502,22 +6488,12 @@
       </c>
       <c r="H103" s="7" t="inlineStr">
         <is>
-          <t>S9</t>
-        </is>
-      </c>
-      <c r="I103" s="7" t="inlineStr">
-        <is>
           <t>S6</t>
         </is>
       </c>
-      <c r="J103" s="7" t="inlineStr">
-        <is>
-          <t>S5</t>
-        </is>
-      </c>
     </row>
     <row r="104">
-      <c r="A104" s="10" t="inlineStr">
+      <c r="A104" s="11" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -8547,24 +6523,14 @@
           <t>Data</t>
         </is>
       </c>
-      <c r="G104" s="10" t="inlineStr">
+      <c r="G104" s="11" t="inlineStr">
         <is>
           <t>0.6</t>
         </is>
       </c>
-      <c r="H104" s="10" t="inlineStr">
-        <is>
-          <t>S9</t>
-        </is>
-      </c>
-      <c r="I104" s="10" t="inlineStr">
+      <c r="H104" s="11" t="inlineStr">
         <is>
           <t>S6</t>
-        </is>
-      </c>
-      <c r="J104" s="10" t="inlineStr">
-        <is>
-          <t>S5</t>
         </is>
       </c>
     </row>
@@ -8606,69 +6572,49 @@
       </c>
       <c r="H105" s="7" t="inlineStr">
         <is>
-          <t>S9</t>
-        </is>
-      </c>
-      <c r="I105" s="7" t="inlineStr">
-        <is>
           <t>S6</t>
         </is>
       </c>
-      <c r="J105" s="7" t="inlineStr">
-        <is>
-          <t>S5</t>
-        </is>
-      </c>
     </row>
     <row r="106">
-      <c r="A106" s="10" t="inlineStr">
+      <c r="A106" s="11" t="inlineStr">
         <is>
           <t>102</t>
         </is>
       </c>
       <c r="B106" s="9" t="inlineStr">
         <is>
-          <t>Weight calculated from footage</t>
+          <t>Machine commissioning support</t>
         </is>
       </c>
       <c r="C106" s="9" t="inlineStr">
         <is>
-          <t>Weight is derived from footage and cross-section rather than a scale, because flat wire is produced continuously and not weighed during the run.</t>
+          <t>The system is switched from simulation to live machine control with engineering support on hand, so the mill is configured by the application rather than by hand.</t>
         </is>
       </c>
       <c r="D106" s="9" t="inlineStr">
         <is>
-          <t>Yield, cost and scrap</t>
+          <t>Integration testing, commissioning and go-live</t>
         </is>
       </c>
       <c r="E106" s="9" t="inlineStr">
         <is>
-          <t>Production control</t>
+          <t>Commissioning and controls engineering</t>
         </is>
       </c>
       <c r="F106" s="9" t="inlineStr">
         <is>
-          <t>Operator screens + Application services</t>
-        </is>
-      </c>
-      <c r="G106" s="10" t="inlineStr">
-        <is>
-          <t>4.1</t>
-        </is>
-      </c>
-      <c r="H106" s="10" t="inlineStr">
-        <is>
-          <t>S9</t>
-        </is>
-      </c>
-      <c r="I106" s="10" t="inlineStr">
-        <is>
-          <t>S6</t>
-        </is>
-      </c>
-      <c r="J106" s="10" t="inlineStr">
-        <is>
-          <t>S5</t>
+          <t>Live data and machine interface</t>
+        </is>
+      </c>
+      <c r="G106" s="11" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="H106" s="11" t="inlineStr">
+        <is>
+          <t>S7</t>
         </is>
       </c>
     </row>
@@ -8680,260 +6626,42 @@
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>Yield attributed per source rod</t>
+          <t>Defect resolution allowance</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>Yield is attributed across weld points to each source rod, so welding-wire certificates carry correct per-rod figures.</t>
+          <t>Time is budgeted to fix what the end-to-end runs find, so defects are closed before the trial rather than carried into it.</t>
         </is>
       </c>
       <c r="D107" s="6" t="inlineStr">
         <is>
-          <t>Yield, cost and scrap</t>
+          <t>Integration testing, commissioning and go-live</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
         <is>
-          <t>Quality and production control</t>
+          <t>Quality assurance</t>
         </is>
       </c>
       <c r="F107" s="6" t="inlineStr">
         <is>
-          <t>Application services</t>
+          <t>Operator screens + Application services + Data</t>
         </is>
       </c>
       <c r="G107" s="7" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="H107" s="7" t="inlineStr">
         <is>
-          <t>S10</t>
-        </is>
-      </c>
-      <c r="I107" s="7" t="inlineStr">
-        <is>
-          <t>S6</t>
-        </is>
-      </c>
-      <c r="J107" s="7" t="inlineStr">
-        <is>
-          <t>S5</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="10" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="B108" s="9" t="inlineStr">
-        <is>
-          <t>Flat wire cost standards</t>
-        </is>
-      </c>
-      <c r="C108" s="9" t="inlineStr">
-        <is>
-          <t>Cost standards exist for the new lines, so costing reports are populated rather than blank.</t>
-        </is>
-      </c>
-      <c r="D108" s="9" t="inlineStr">
-        <is>
-          <t>Yield, cost and scrap</t>
-        </is>
-      </c>
-      <c r="E108" s="9" t="inlineStr">
-        <is>
-          <t>Cost accounting</t>
-        </is>
-      </c>
-      <c r="F108" s="9" t="inlineStr">
-        <is>
-          <t>Application services + Operator screens + Data</t>
-        </is>
-      </c>
-      <c r="G108" s="10" t="inlineStr">
-        <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="H108" s="10" t="inlineStr">
-        <is>
-          <t>S10</t>
-        </is>
-      </c>
-      <c r="I108" s="10" t="inlineStr">
-        <is>
-          <t>S6</t>
-        </is>
-      </c>
-      <c r="J108" s="10" t="inlineStr">
-        <is>
-          <t>S5</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="7" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="B109" s="6" t="inlineStr">
-        <is>
-          <t>Scrap outlet selection</t>
-        </is>
-      </c>
-      <c r="C109" s="6" t="inlineStr">
-        <is>
-          <t>Flat wire scrap is routed to the right outlet and handled like every other material.</t>
-        </is>
-      </c>
-      <c r="D109" s="6" t="inlineStr">
-        <is>
-          <t>Yield, cost and scrap</t>
-        </is>
-      </c>
-      <c r="E109" s="6" t="inlineStr">
-        <is>
-          <t>Production control</t>
-        </is>
-      </c>
-      <c r="F109" s="6" t="inlineStr">
-        <is>
-          <t>Operator screens + Application services + Data</t>
-        </is>
-      </c>
-      <c r="G109" s="7" t="inlineStr">
-        <is>
-          <t>2.1</t>
-        </is>
-      </c>
-      <c r="H109" s="7" t="inlineStr">
-        <is>
-          <t>S10</t>
-        </is>
-      </c>
-      <c r="I109" s="7" t="inlineStr">
-        <is>
-          <t>S6</t>
-        </is>
-      </c>
-      <c r="J109" s="7" t="inlineStr">
-        <is>
-          <t>S5</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="10" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="B110" s="9" t="inlineStr">
-        <is>
-          <t>Machine commissioning support</t>
-        </is>
-      </c>
-      <c r="C110" s="9" t="inlineStr">
-        <is>
-          <t>The system is switched from simulation to live machine control with engineering support on hand, so the mill is configured by the application rather than by hand.</t>
-        </is>
-      </c>
-      <c r="D110" s="9" t="inlineStr">
-        <is>
-          <t>Integration testing, commissioning and go-live</t>
-        </is>
-      </c>
-      <c r="E110" s="9" t="inlineStr">
-        <is>
-          <t>Commissioning and controls engineering</t>
-        </is>
-      </c>
-      <c r="F110" s="9" t="inlineStr">
-        <is>
-          <t>Live data and machine interface</t>
-        </is>
-      </c>
-      <c r="G110" s="10" t="inlineStr">
-        <is>
-          <t>4.4</t>
-        </is>
-      </c>
-      <c r="H110" s="10" t="inlineStr">
-        <is>
-          <t>S10</t>
-        </is>
-      </c>
-      <c r="I110" s="10" t="inlineStr">
-        <is>
           <t>S7</t>
         </is>
       </c>
-      <c r="J110" s="10" t="inlineStr">
-        <is>
-          <t>S5</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="7" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="B111" s="6" t="inlineStr">
-        <is>
-          <t>Defect resolution allowance</t>
-        </is>
-      </c>
-      <c r="C111" s="6" t="inlineStr">
-        <is>
-          <t>Time is budgeted to fix what the end-to-end runs find, so defects are closed before the trial rather than carried into it.</t>
-        </is>
-      </c>
-      <c r="D111" s="6" t="inlineStr">
-        <is>
-          <t>Integration testing, commissioning and go-live</t>
-        </is>
-      </c>
-      <c r="E111" s="6" t="inlineStr">
-        <is>
-          <t>Quality assurance</t>
-        </is>
-      </c>
-      <c r="F111" s="6" t="inlineStr">
-        <is>
-          <t>Operator screens + Application services + Data</t>
-        </is>
-      </c>
-      <c r="G111" s="7" t="inlineStr">
-        <is>
-          <t>4.4</t>
-        </is>
-      </c>
-      <c r="H111" s="7" t="inlineStr">
-        <is>
-          <t>S10</t>
-        </is>
-      </c>
-      <c r="I111" s="7" t="inlineStr">
-        <is>
-          <t>S7</t>
-        </is>
-      </c>
-      <c r="J111" s="7" t="inlineStr">
-        <is>
-          <t>S5</t>
-        </is>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J111"/>
+  <autoFilter ref="A4:H107"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8945,14 +6673,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="100" customWidth="1" min="5" max="5"/>
+    <col width="100" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -8984,20 +6710,10 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Reached with 2 developers</t>
+          <t>Reached</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>Reached with 3 developers</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>Reached with 4 developers</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>What it means</t>
         </is>
@@ -9011,20 +6727,10 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>S4 · 16 Oct 2026</t>
+          <t>S3 · 02 Oct 2026</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>S3 · 02 Oct 2026</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>S2 · 18 Sep 2026</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>Screen framework, application services and database in place, with the machine-write layer running in simulation. Everything after this point is feature work.</t>
         </is>
@@ -9036,22 +6742,12 @@
           <t>First live end-to-end slice</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>S4 · 16 Oct 2026</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>S3 · 02 Oct 2026</t>
         </is>
       </c>
-      <c r="D7" s="10" t="inlineStr">
-        <is>
-          <t>S2 · 18 Sep 2026</t>
-        </is>
-      </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="C7" s="11" t="inlineStr">
         <is>
           <t>Machine data reaching a live line status board. The first point at which the system can be seen working against real equipment data.</t>
         </is>
@@ -9065,20 +6761,10 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>S6 · 13 Nov 2026</t>
+          <t>S4 · 16 Oct 2026</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>S4 · 16 Oct 2026</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>S3 · 02 Oct 2026</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>Check in a rod, configure the machine, watch the run live, record events against it. The core operator experience end to end.</t>
         </is>
@@ -9090,22 +6776,12 @@
           <t>All three production routes complete</t>
         </is>
       </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>S8 · 11 Dec 2026</t>
-        </is>
-      </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>S6 · 13 Nov 2026</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
-        <is>
-          <t>S4 · 16 Oct 2026</t>
-        </is>
-      </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="C9" s="11" t="inlineStr">
         <is>
           <t>Standalone drawing, standalone finishing and the hybrid route, through to a finished coil with its traceability and label.</t>
         </is>
@@ -9119,27 +6795,17 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>S10 · 08 Jan 2027</t>
+          <t>S7 · 25 Nov 2026</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>S7 · 25 Nov 2026</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>S5 · 30 Oct 2026</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
           <t>All planned scope built and internally tested. Acceptance testing and machine commissioning follow this date; they are not included in it.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>Stages overlap, so two milestones can land in the same sprint — the plan does not idle between them.</t>
         </is>
@@ -9434,7 +7100,7 @@
       <c r="C9" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">None of the three team sizes completes development by the end of September. The dates on the options sheet are the honest consequence. </t>
+            <t xml:space="preserve">Three developers do not complete development by the end of September — the work needs about four people sustained, and the sprints start on 24 August, which removes the run-up from the available capacity. The date on the summary sheet is the honest consequence. </t>
           </r>
           <r>
             <rPr>

--- a/MVP-1/SRS/FlatWire_DevelopmentPlan.xlsx
+++ b/MVP-1/SRS/FlatWire_DevelopmentPlan.xlsx
@@ -557,7 +557,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Issued August 13, 2026 · 14 stages · 103 work items · 174 days of development effort</t>
+          <t>Issued August 13, 2026 · 14 stages · 103 work items · 170 days of development effort</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
               <b val="1"/>
               <sz val="11"/>
             </rPr>
-            <t>174 days of development effort</t>
+            <t>170 days of development effort</t>
           </r>
           <r>
             <t xml:space="preserve"> across </t>
@@ -929,7 +929,7 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>174 days of development effort across 103 work items — the plan below is what that delivers, and when.</t>
+          <t>170 days of development effort across 103 work items — the plan below is what that delivers, and when.</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
@@ -1796,7 +1796,7 @@
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>Stage effort is rounded to whole days, so the column sums to within a day of the 174-day total rather than exactly to it.</t>
+          <t>Stage effort is rounded to whole days, so the column sums to within a day of the 170-day total rather than exactly to it.</t>
         </is>
       </c>
     </row>
@@ -3434,12 +3434,12 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>Existing scheduling system extended for flat wire</t>
+          <t>CANCELLED — existing scheduling system extended for flat wire</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>Flat wire fits alongside coil in the systems the plant already runs — receiving, planning, scheduling, reporting, yield and costing — without ambiguity, and nothing that reads them today breaks.</t>
+          <t>CANCELLED August 18, 2026 at your direction — there will be no changes to the existing scheduling system's database. Flat wire is tracked entirely within the new flat wire module, and the systems the plant already runs are read and written exactly as they stand today. This removes the largest single risk in the plan.</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
@@ -3459,7 +3459,7 @@
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="H31" s="7" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>In-process status for flat wire material</t>
+          <t>CANCELLED — in-process status for flat wire material</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>Material actively on a flattening line is distinctly tracked and cannot be double-allocated.</t>
+          <t>CANCELLED August 18, 2026, with the change above. Material actively on a flattening line is still distinctly tracked and still cannot be double-allocated — the status is simply held on the flat wire module's own rod and spool records rather than added to the existing scheduling system.</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="G32" s="11" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="H32" s="11" t="inlineStr">
